--- a/data/trans_bre/P38A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 16,31</t>
+          <t>2,87; 16,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 17,63</t>
+          <t>3,3; 17,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 24,49</t>
+          <t>2,29; 25,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 32,12</t>
+          <t>5,0; 31,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 32,6</t>
+          <t>5,21; 31,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 56,14</t>
+          <t>3,66; 56,18</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,11</t>
+          <t>1,54; 10,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 16,03</t>
+          <t>7,15; 16,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 10,08</t>
+          <t>-30,84; 9,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,92</t>
+          <t>1,87; 12,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,03</t>
+          <t>9,12; 22,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 14,15</t>
+          <t>-41,46; 13,23</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,77</t>
+          <t>3,81; 10,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 11,24</t>
+          <t>2,87; 10,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,44</t>
+          <t>1,32; 9,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,86</t>
+          <t>4,27; 13,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 14,23</t>
+          <t>3,4; 13,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,93</t>
+          <t>1,57; 11,87</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,41</t>
+          <t>-5,08; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,29</t>
+          <t>0,68; 7,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 68,92</t>
+          <t>3,25; 63,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,54</t>
+          <t>-5,43; 1,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,47</t>
+          <t>0,76; 8,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 285,15</t>
+          <t>3,57; 206,63</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,45</t>
+          <t>-2,81; 3,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,26</t>
+          <t>-1,76; 4,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,82</t>
+          <t>-0,36; 5,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,72</t>
+          <t>-2,91; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,63</t>
+          <t>-1,85; 4,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,31</t>
+          <t>-0,38; 5,54</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 1,15</t>
+          <t>-4,73; 0,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,11</t>
+          <t>-1,2; 2,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,24</t>
+          <t>0,32; 4,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 1,18</t>
+          <t>-4,77; 0,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,26</t>
+          <t>-1,21; 3,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,48</t>
+          <t>0,32; 4,43</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,36</t>
+          <t>-0,55; 4,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,63</t>
+          <t>-1,73; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -0,16</t>
+          <t>-4,07; -0,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,63</t>
+          <t>-0,55; 4,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,74</t>
+          <t>-1,75; 2,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,17</t>
+          <t>-4,13; -0,12</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,03</t>
+          <t>2,69; 6,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,97</t>
+          <t>4,72; 8,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 28,77</t>
+          <t>3,27; 28,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,16</t>
+          <t>3,12; 7,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,68</t>
+          <t>5,59; 9,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 46,0</t>
+          <t>3,87; 47,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 16,5</t>
+          <t>2,61; 15,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 17,05</t>
+          <t>3,93; 17,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 25,18</t>
+          <t>4,78; 24,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 31,5</t>
+          <t>4,53; 30,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 31,73</t>
+          <t>6,34; 32,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 56,18</t>
+          <t>8,22; 57,68</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,47%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 10,2</t>
+          <t>1,92; 9,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 16,09</t>
+          <t>6,85; 15,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 9,65</t>
+          <t>0,57; 13,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 12,97</t>
+          <t>2,3; 12,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 22,03</t>
+          <t>8,77; 22,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 13,23</t>
+          <t>0,83; 20,77</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,91</t>
+          <t>4,26; 10,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 10,38</t>
+          <t>2,87; 10,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,32</t>
+          <t>3,18; 11,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 13,06</t>
+          <t>4,84; 12,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 13,15</t>
+          <t>3,39; 13,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,87</t>
+          <t>3,88; 15,51</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,88</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,74</t>
+          <t>-4,81; 1,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,41</t>
+          <t>-0,07; 7,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 63,43</t>
+          <t>0,23; 5,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,88</t>
+          <t>-5,12; 1,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,66</t>
+          <t>-0,08; 8,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 206,63</t>
+          <t>0,25; 6,7</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,41</t>
+          <t>-2,97; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,43</t>
+          <t>-2,06; 4,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 5,09</t>
+          <t>0,55; 5,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,63</t>
+          <t>-3,06; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,85</t>
+          <t>-2,17; 4,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,54</t>
+          <t>0,58; 6,38</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,91</t>
+          <t>-4,82; 0,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,9</t>
+          <t>-1,44; 2,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,22</t>
+          <t>-0,32; 3,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,97</t>
+          <t>-4,85; 0,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,04</t>
+          <t>-1,46; 3,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,43</t>
+          <t>-0,33; 3,5</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,05%</t>
+          <t>-2,32%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,56</t>
+          <t>-0,53; 4,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,61</t>
+          <t>-1,72; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; -0,11</t>
+          <t>-4,25; -0,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,84</t>
+          <t>-0,53; 4,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,7</t>
+          <t>-1,74; 2,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,12</t>
+          <t>-4,29; -0,3</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,04</t>
+          <t>2,72; 5,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,12</t>
+          <t>4,54; 7,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 28,16</t>
+          <t>3,9; 7,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,16</t>
+          <t>3,12; 6,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,86</t>
+          <t>5,38; 9,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 47,1</t>
+          <t>4,65; 9,71</t>
         </is>
       </c>
     </row>
